--- a/output/pdf_financials_xlsx/WILD.xlsx
+++ b/output/pdf_financials_xlsx/WILD.xlsx
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.026</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.068</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.183</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -2103,13 +2103,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.304</v>
+        <v>-1.236</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.63</v>
+        <v>1.813</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>3.98</v>
@@ -2223,13 +2223,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>4.492</v>
+        <v>4.518</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.228</v>
+        <v>-0.16</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.579</v>
+        <v>2.762</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>4.818</v>
@@ -2283,13 +2283,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>7.248785683164163</v>
+        <v>7.290742145266181</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-0.5633663610980703</v>
+        <v>-0.3953448148056633</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.654478514320778</v>
+        <v>4.984749769892978</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>6.63207014742522</v>
@@ -2469,28 +2469,26 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>10.806</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>17.276</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>19.525</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>19.166</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>12.64</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>26.679</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>42.907</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>80.446</v>
@@ -2499,28 +2497,28 @@
         <v>62.143</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>46.55</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>39.999</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>67.889</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>78.431</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>59.899</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>80.348</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>49.715</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>68.871</v>
       </c>
     </row>
     <row r="35">
@@ -2588,25 +2586,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.272</v>
+        <v>11.078</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>6.098</v>
+        <v>23.374</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>6.06</v>
+        <v>25.585</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>3.323</v>
+        <v>22.489</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>12.64</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>26.679</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>42.907</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>80.446</v>
@@ -2615,28 +2613,28 @@
         <v>62.143</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>46.55</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>39.999</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>67.889</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>78.431</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>59.899</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>80.348</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>49.715</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>68.871</v>
       </c>
     </row>
     <row r="37">
@@ -3307,22 +3305,22 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>48.464</v>
+        <v>31.188</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>59.589</v>
+        <v>40.064</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>64.91</v>
+        <v>45.744</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>133.675</v>
+        <v>121.035</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>178.35</v>
+        <v>151.671</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>259.211</v>
+        <v>216.304</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>247.531</v>
@@ -3331,28 +3329,28 @@
         <v>445.149</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>241.138</v>
+        <v>194.588</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>195.742</v>
+        <v>155.743</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>233.853</v>
+        <v>165.964</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>246.024</v>
+        <v>167.593</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>240.88</v>
+        <v>180.981</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>509.331</v>
+        <v>428.983</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>219.872</v>
+        <v>170.157</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>179.418</v>
+        <v>110.547</v>
       </c>
     </row>
     <row r="49">
@@ -8006,10 +8004,10 @@
         <v>0</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-4.93</v>
       </c>
       <c r="I124" s="3" t="n">
         <v>0</v>
@@ -8064,10 +8062,10 @@
         <v>47.918</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>24.19</v>
+        <v>24.12</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-4.93</v>
       </c>
       <c r="I125" s="3" t="n">
         <v>94.119</v>
@@ -8859,7 +8857,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -45425,7 +45423,11 @@
           <t>Repayment of bank indebtedness</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
@@ -70731,7 +70733,7 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E632" s="5" t="n">
@@ -70832,7 +70834,7 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E633" s="5" t="n">

--- a/output/pdf_financials_xlsx/WILD.xlsx
+++ b/output/pdf_financials_xlsx/WILD.xlsx
@@ -6597,55 +6597,55 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>1.274</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>1.076</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.949</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.838</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>2.646</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>3.824</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>6.709</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>10.033</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>11.379</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>15.346</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>14.32</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>10.14</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>10.542</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>10.601</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>12.862</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>12.811</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>9.176</v>
       </c>
     </row>
     <row r="101">
@@ -7305,7 +7305,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>5.214</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -7769,10 +7769,10 @@
         <v>0</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0</v>
+        <v>16.745</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0</v>
+        <v>36.588</v>
       </c>
       <c r="H120" s="3" t="n">
         <v>0</v>
@@ -28200,7 +28200,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -33416,7 +33416,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -43661,7 +43661,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E358" s="5" t="n">
@@ -46999,7 +46999,11 @@
           <t>Proceeds from issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -49759,7 +49763,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/WILD.xlsx
+++ b/output/pdf_financials_xlsx/WILD.xlsx
@@ -3815,52 +3815,52 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>15.825</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>19.231</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>19.542</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>16.805</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>25.46</v>
       </c>
       <c r="H56" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>39.708</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>58.397</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>66.569</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>63.491</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>111.682</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0</v>
+        <v>117.415</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0</v>
+        <v>123.143</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0</v>
+        <v>129.342</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0</v>
+        <v>133.357</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>0</v>
+        <v>137.927</v>
       </c>
     </row>
     <row r="57">
@@ -3875,52 +3875,52 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>9.423999999999999</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>11.124</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>12.066</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>14.157</v>
       </c>
       <c r="H57" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>22.345</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>27.689</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>36.517</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0</v>
+        <v>44.579</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>0</v>
+        <v>58.531</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>0</v>
+        <v>70.913</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>0</v>
+        <v>84.291</v>
       </c>
       <c r="P57" s="3" t="n">
-        <v>0</v>
+        <v>95.985</v>
       </c>
       <c r="Q57" s="3" t="n">
-        <v>0</v>
+        <v>108.181</v>
       </c>
       <c r="R57" s="3" t="n">
-        <v>0</v>
+        <v>118.464</v>
       </c>
     </row>
     <row r="58">
@@ -4353,19 +4353,19 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>2.961</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>5.082</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.728</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>6.044</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>8.08</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0</v>
@@ -4386,19 +4386,19 @@
         <v>0</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>130.299</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>161.849</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>38.925</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>35.638</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>31.829</v>
       </c>
     </row>
     <row r="65">
@@ -4533,19 +4533,19 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>9.519</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>10.829</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>13.291</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>39.888</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>53.694</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0</v>
@@ -4572,10 +4572,10 @@
         <v>0</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>129.718</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="R67" s="3" t="n">
         <v>0</v>
@@ -4627,7 +4627,7 @@
         <v>130.299</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0</v>
+        <v>161.849</v>
       </c>
       <c r="P68" s="3" t="n">
         <v>171.464</v>
@@ -5043,7 +5043,7 @@
         <v>65.40300000000001</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>274.278</v>
+        <v>112.429</v>
       </c>
       <c r="P75" s="3" t="n">
         <v>93.89100000000001</v>
@@ -6957,43 +6957,43 @@
         <v>0</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-1.492</v>
+        <v>-12.275</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>-5.328</v>
       </c>
       <c r="H106" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>-25.646</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>12.83</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>-32.012</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0</v>
+        <v>-31.138</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0</v>
+        <v>38.53</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0</v>
+        <v>14.878</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0</v>
+        <v>-48.42</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0</v>
+        <v>4.401</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0</v>
+        <v>-20.234</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>0</v>
+        <v>28.353</v>
       </c>
     </row>
     <row r="107">
@@ -7204,10 +7204,10 @@
         <v>0</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>2.276</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>3.098</v>
       </c>
       <c r="M110" s="3" t="n">
         <v>0</v>
@@ -7546,34 +7546,34 @@
         <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-17.943</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-4.332</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-8.539</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-4.252</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-1.875</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-3.467</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-7.544</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0</v>
+        <v>-6.086</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>0</v>
+        <v>-1.964</v>
       </c>
       <c r="R116" s="3" t="n">
-        <v>0</v>
+        <v>-1.588</v>
       </c>
     </row>
     <row r="117">
@@ -11669,7 +11669,11 @@
           <t>Write-down of investment in film and television programs, acquired and library content, intangible assets and goodwill (note 18)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -29182,7 +29186,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -29776,7 +29784,11 @@
           <t>Net change in non-cash balances related to operations (note 26)</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -31425,7 +31437,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -32458,7 +32474,11 @@
           <t>Net change in non-cash balances related to operations (note 24)</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -33044,7 +33064,11 @@
           <t>Acquisition of intangible assets (note 10)</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -34247,7 +34271,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -34809,7 +34837,11 @@
           <t>Net change in non-cash balances related to operations (note 25)</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -35951,7 +35983,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -36921,7 +36957,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -37220,7 +37260,11 @@
           <t>Net change in non-cash balances related to operations (note 24)</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -39923,7 +39967,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -40319,7 +40367,11 @@
           <t>Net change in non-cash balances related to operations (note 23)</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -41396,7 +41448,11 @@
           <t>Net change in non-cash balances related to operations (note 22)</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
@@ -42283,7 +42339,11 @@
           <t>Acquisition/cost of intangible assets</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
           <t>-</t>
@@ -44845,7 +44905,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
           <t>-</t>
@@ -46803,7 +46867,11 @@
           <t>Net change in non-cash balances related to operations (note 22)</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -51947,7 +52015,11 @@
           <t>Recovery of future income taxes</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E442" t="inlineStr">
         <is>
           <t>-</t>
@@ -53341,7 +53413,11 @@
           <t>Provision for (recovery of) future income taxes</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E456" s="5" t="n">
         <v>0.535</v>
       </c>
